--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,337 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122979174</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>481032</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6790798</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122963066</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78502</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>480927</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6790653</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122979345</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>480997</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6790785</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På Gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122914542</v>
+        <v>122911045</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,51 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481006</v>
+        <v>480974</v>
       </c>
       <c r="R2" t="n">
-        <v>6790782</v>
+        <v>6790698</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122911045</v>
+        <v>122914542</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,37 +803,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480974</v>
+        <v>481006</v>
       </c>
       <c r="R3" t="n">
-        <v>6790698</v>
+        <v>6790782</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122911045</v>
+        <v>122914542</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480974</v>
+        <v>481006</v>
       </c>
       <c r="R2" t="n">
-        <v>6790698</v>
+        <v>6790782</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122914542</v>
+        <v>122911045</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,51 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481006</v>
+        <v>480974</v>
       </c>
       <c r="R3" t="n">
-        <v>6790782</v>
+        <v>6790698</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122963066</v>
+        <v>122979345</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480927</v>
+        <v>480997</v>
       </c>
       <c r="R5" t="n">
-        <v>6790653</v>
+        <v>6790785</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122979345</v>
+        <v>122963066</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480997</v>
+        <v>480927</v>
       </c>
       <c r="R6" t="n">
-        <v>6790785</v>
+        <v>6790653</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1202,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122914542</v>
+        <v>122911045</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,51 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481006</v>
+        <v>480974</v>
       </c>
       <c r="R2" t="n">
-        <v>6790782</v>
+        <v>6790698</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122911045</v>
+        <v>122914542</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,37 +803,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480974</v>
+        <v>481006</v>
       </c>
       <c r="R3" t="n">
-        <v>6790698</v>
+        <v>6790782</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122979174</v>
+        <v>122979345</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -949,17 +949,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481032</v>
+        <v>480997</v>
       </c>
       <c r="R4" t="n">
-        <v>6790798</v>
+        <v>6790785</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,9 +986,24 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122979345</v>
+        <v>122963066</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480997</v>
+        <v>480927</v>
       </c>
       <c r="R5" t="n">
-        <v>6790785</v>
+        <v>6790653</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1090,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122963066</v>
+        <v>122979174</v>
       </c>
       <c r="B6" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,37 +1158,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480927</v>
+        <v>481032</v>
       </c>
       <c r="R6" t="n">
-        <v>6790653</v>
+        <v>6790798</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,19 +1215,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122979345</v>
+        <v>122963066</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480997</v>
+        <v>480927</v>
       </c>
       <c r="R4" t="n">
-        <v>6790785</v>
+        <v>6790653</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122963066</v>
+        <v>122979345</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480927</v>
+        <v>480997</v>
       </c>
       <c r="R5" t="n">
-        <v>6790653</v>
+        <v>6790785</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1105,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122911045</v>
+        <v>122914542</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480974</v>
+        <v>481006</v>
       </c>
       <c r="R2" t="n">
-        <v>6790698</v>
+        <v>6790782</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122914542</v>
+        <v>122911045</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,51 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481006</v>
+        <v>480974</v>
       </c>
       <c r="R3" t="n">
-        <v>6790782</v>
+        <v>6790698</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122963066</v>
+        <v>122979345</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480927</v>
+        <v>480997</v>
       </c>
       <c r="R4" t="n">
-        <v>6790653</v>
+        <v>6790785</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122979345</v>
+        <v>122979174</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1061,17 +1066,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480997</v>
+        <v>481032</v>
       </c>
       <c r="R5" t="n">
-        <v>6790785</v>
+        <v>6790798</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,24 +1103,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122979174</v>
+        <v>122963066</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,37 +1148,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481032</v>
+        <v>480927</v>
       </c>
       <c r="R6" t="n">
-        <v>6790798</v>
+        <v>6790653</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,9 +1205,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122914542</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>122911045</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>122979345</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122979174</v>
+        <v>122963066</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78505</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,37 +1046,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481032</v>
+        <v>480927</v>
       </c>
       <c r="R5" t="n">
-        <v>6790798</v>
+        <v>6790653</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,9 +1103,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122963066</v>
+        <v>122979174</v>
       </c>
       <c r="B6" t="n">
-        <v>78502</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,37 +1158,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480927</v>
+        <v>481032</v>
       </c>
       <c r="R6" t="n">
-        <v>6790653</v>
+        <v>6790798</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,19 +1215,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122911045</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>122979345</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122963066</v>
+        <v>122979174</v>
       </c>
       <c r="B5" t="n">
-        <v>78505</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,37 +1046,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480927</v>
+        <v>481032</v>
       </c>
       <c r="R5" t="n">
-        <v>6790653</v>
+        <v>6790798</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,19 +1103,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122979174</v>
+        <v>122963066</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>78507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,37 +1148,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481032</v>
+        <v>480927</v>
       </c>
       <c r="R6" t="n">
-        <v>6790798</v>
+        <v>6790653</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,9 +1205,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122911045</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>122979345</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>122979174</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>122963066</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
+        <v>78508</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122911045</v>
+        <v>122914542</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>57640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480974</v>
+        <v>481006</v>
       </c>
       <c r="R2" t="n">
-        <v>6790698</v>
+        <v>6790782</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122914542</v>
+        <v>122911045</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,51 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481006</v>
+        <v>480974</v>
       </c>
       <c r="R3" t="n">
-        <v>6790782</v>
+        <v>6790698</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +916,7 @@
         <v>122979174</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>122963066</v>
       </c>
       <c r="B5" t="n">
-        <v>78511</v>
+        <v>78517</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>122979345</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,6 +1242,113 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125314704</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>480981</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6790756</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>125314704</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1247,12 +1247,7 @@
         <v>125314704</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>125314704</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>125314704</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>125314704</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,6 +1344,324 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128930958</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79152</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>185</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Höghedserget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>480983</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6790743</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128930966</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79152</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>185</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Höghedserget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>480985</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6790736</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128930977</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79152</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Höghedserget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480992</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6790785</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1349,7 +1349,7 @@
         <v>128930958</v>
       </c>
       <c r="B8" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128930966</v>
       </c>
       <c r="B9" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128930977</v>
       </c>
       <c r="B10" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1349,7 +1349,7 @@
         <v>128930958</v>
       </c>
       <c r="B8" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128930966</v>
       </c>
       <c r="B9" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128930977</v>
       </c>
       <c r="B10" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1349,7 +1349,7 @@
         <v>128930958</v>
       </c>
       <c r="B8" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128930966</v>
       </c>
       <c r="B9" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128930977</v>
       </c>
       <c r="B10" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1349,7 +1349,7 @@
         <v>128930958</v>
       </c>
       <c r="B8" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128930966</v>
       </c>
       <c r="B9" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128930977</v>
       </c>
       <c r="B10" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1349,7 +1349,7 @@
         <v>128930958</v>
       </c>
       <c r="B8" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128930966</v>
       </c>
       <c r="B9" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128930977</v>
       </c>
       <c r="B10" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1349,7 +1349,7 @@
         <v>128930958</v>
       </c>
       <c r="B8" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128930966</v>
       </c>
       <c r="B9" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128930977</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1349,7 +1349,7 @@
         <v>128930958</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128930966</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>128930977</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122914542</v>
+        <v>128930935</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedserget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481006</v>
+        <v>480980</v>
       </c>
       <c r="R2" t="n">
-        <v>6790782</v>
+        <v>6790682</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,33 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122911045</v>
+        <v>128930958</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,34 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedserget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480974</v>
+        <v>480983</v>
       </c>
       <c r="R3" t="n">
-        <v>6790698</v>
+        <v>6790743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,33 +868,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122979174</v>
+        <v>128930966</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,34 +898,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedserget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481032</v>
+        <v>480985</v>
       </c>
       <c r="R4" t="n">
-        <v>6790798</v>
+        <v>6790736</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,12 +955,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,33 +974,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122963066</v>
+        <v>128930977</v>
       </c>
       <c r="B5" t="n">
-        <v>78517</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,37 +1004,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedserget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480927</v>
+        <v>480992</v>
       </c>
       <c r="R5" t="n">
-        <v>6790653</v>
+        <v>6790785</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1061,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,33 +1080,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122979345</v>
+        <v>128930934</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1110,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedserget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480997</v>
+        <v>480990</v>
       </c>
       <c r="R6" t="n">
-        <v>6790785</v>
+        <v>6790657</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,27 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,28 +1181,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125314704</v>
+        <v>122911045</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480981</v>
+        <v>480974</v>
       </c>
       <c r="R7" t="n">
-        <v>6790756</v>
+        <v>6790698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,17 +1265,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,60 +1295,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128930958</v>
+        <v>122911058</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Höghedserget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480983</v>
+        <v>481029</v>
       </c>
       <c r="R8" t="n">
-        <v>6790743</v>
+        <v>6790791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,17 +1372,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,67 +1396,63 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128930966</v>
+        <v>122911334</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Höghedserget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480985</v>
+        <v>481021</v>
       </c>
       <c r="R9" t="n">
-        <v>6790736</v>
+        <v>6790761</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,17 +1479,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,67 +1503,63 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128930977</v>
+        <v>122912733</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Höghedserget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480992</v>
+        <v>480886</v>
       </c>
       <c r="R10" t="n">
-        <v>6790785</v>
+        <v>6790630</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,17 +1586,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,22 +1600,1517 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122914812</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>480982</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6790653</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122915141</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>480999</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6790659</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122915163</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>480988</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6790673</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122964690</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>481000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6790687</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122979174</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>481032</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6790798</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122979345</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>480997</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6790785</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På Gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132631787</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>480948</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6790711</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Christer Lindberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Christer Lindberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122963066</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>480927</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6790653</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122914576</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>480927</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6790599</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122913380</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>481029</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6790791</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122964814</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>481000</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6790685</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Betad tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122914542</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>481006</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6790782</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125314704</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>480981</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6790756</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128930975</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Höghedserget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>480992</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6790785</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Peter Turander</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Peter Turander</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930935</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930958</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930966</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930977</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930934</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945114</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945115</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911045</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911058</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911334</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122912733</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914812</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915141</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915163</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2231,6 +2306,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122964690</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2328,6 +2408,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122979174</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2440,6 +2525,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122979345</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2547,6 +2637,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945108</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2654,6 +2749,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945110</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2761,6 +2861,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945113</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2868,6 +2973,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945111</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2975,6 +3085,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132631787</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3082,6 +3197,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122963066</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3189,6 +3309,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945149</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3296,6 +3421,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914576</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3408,6 +3538,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945150</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3523,6 +3658,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913380</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3643,6 +3783,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122964814</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3755,6 +3900,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945107</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3876,6 +4026,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914542</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3978,6 +4133,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125314704</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4085,6 +4245,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945112</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4191,6 +4356,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128930975</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4299,8 +4469,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945109</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 7618-2025 artfynd.xlsx
+++ b/artfynd/A 7618-2025 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>134945114</v>
       </c>
       <c r="B7" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>134945115</v>
       </c>
       <c r="B8" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>134945108</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>134945110</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>134945113</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>134945111</v>
       </c>
       <c r="B22" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>134945149</v>
       </c>
       <c r="B25" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>134945150</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>134945107</v>
       </c>
       <c r="B30" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>134945112</v>
       </c>
       <c r="B33" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>134945109</v>
       </c>
       <c r="B35" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
